--- a/xls/square_high_un_16_tri3_19.xlsx
+++ b/xls/square_high_un_16_tri3_19.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>485</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>340</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>380</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>2070</v>
+      </c>
+      <c r="I17">
+        <v>-2.034444506270362</v>
+      </c>
+      <c r="J17">
+        <v>-1.9825018996606478</v>
+      </c>
+      <c r="K17">
+        <v>-0.7133041368285776</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>485</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>340</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>435</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>2388</v>
+      </c>
+      <c r="I18">
+        <v>-2.279759136361316</v>
+      </c>
+      <c r="J18">
+        <v>-1.8175463370282472</v>
+      </c>
+      <c r="K18">
+        <v>0.24914164776502398</v>
+      </c>
+    </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
